--- a/numbers.xlsx
+++ b/numbers.xlsx
@@ -8,13 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/syc/Documents/GitHub/godotquarium/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F5F1DD0D-DA70-3E4A-8F5D-57B44F939BD2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A40AAA9B-BD0C-F848-8D1A-BA27FC6DC66E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="380" yWindow="500" windowWidth="28040" windowHeight="15120" xr2:uid="{B46BD373-1DB6-C141-9A4E-F1F8F10615B0}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
-    <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
+    <sheet name="Plans" sheetId="3" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId2"/>
+    <sheet name="Sheet2" sheetId="2" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -37,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="165" uniqueCount="124">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="196" uniqueCount="155">
   <si>
     <t>Fish Type / Movement</t>
   </si>
@@ -212,9 +213,6 @@
     </r>
   </si>
   <si>
-    <t>40 / -40</t>
-  </si>
-  <si>
     <r>
       <t>Fast:</t>
     </r>
@@ -228,9 +226,6 @@
     </r>
   </si>
   <si>
-    <t>INF (Global)</t>
-  </si>
-  <si>
     <r>
       <t>Slow:</t>
     </r>
@@ -244,12 +239,6 @@
     </r>
   </si>
   <si>
-    <t>800 to 1000</t>
-  </si>
-  <si>
-    <t>10000 (Dist Sq)</t>
-  </si>
-  <si>
     <r>
       <t>Slow:</t>
     </r>
@@ -263,9 +252,6 @@
     </r>
   </si>
   <si>
-    <t>300 to 500</t>
-  </si>
-  <si>
     <t>Animation State</t>
   </si>
   <si>
@@ -381,6 +367,84 @@
   </si>
   <si>
     <r>
+      <t>32</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> (Initial)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>eating_timer -= 1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> every 2-4 frames</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>hunger_anim_timer</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> check</t>
+    </r>
+  </si>
+  <si>
+    <t>Fishbase</t>
+  </si>
+  <si>
+    <t>Idle Deceleration Multiplier</t>
+  </si>
+  <si>
+    <t>Border</t>
+  </si>
+  <si>
+    <t>Original Pixel Value</t>
+  </si>
+  <si>
+    <t>Logic</t>
+  </si>
+  <si>
+    <t>Left</t>
+  </si>
+  <si>
+    <t>To prevent the nose from clipping the edge.</t>
+  </si>
+  <si>
+    <t>Right</t>
+  </si>
+  <si>
+    <t>(640 total - 20)</t>
+  </si>
+  <si>
+    <t>Top</t>
+  </si>
+  <si>
+    <t>Leaves room for the Menu/Top Bar.</t>
+  </si>
+  <si>
+    <t>Bottom</t>
+  </si>
+  <si>
+    <t>(480 total - 20) Leaves room for the sand.</t>
+  </si>
+  <si>
+    <r>
       <t>0</t>
     </r>
     <r>
@@ -393,7 +457,7 @@
     </r>
     <r>
       <rPr>
-        <sz val="10"/>
+        <sz val="12"/>
         <rFont val="Google Sans Text"/>
         <family val="2"/>
       </rPr>
@@ -414,7 +478,7 @@
     </r>
     <r>
       <rPr>
-        <sz val="10"/>
+        <sz val="12"/>
         <rFont val="Google Sans Text"/>
         <family val="2"/>
       </rPr>
@@ -430,7 +494,7 @@
     </r>
     <r>
       <rPr>
-        <sz val="10"/>
+        <sz val="12"/>
         <rFont val="Google Sans Text"/>
         <family val="2"/>
       </rPr>
@@ -443,7 +507,7 @@
     </r>
     <r>
       <rPr>
-        <sz val="10"/>
+        <sz val="12"/>
         <rFont val="Google Sans Text"/>
         <family val="2"/>
       </rPr>
@@ -464,7 +528,7 @@
     </r>
     <r>
       <rPr>
-        <sz val="10"/>
+        <sz val="12"/>
         <rFont val="Google Sans Text"/>
         <family val="2"/>
       </rPr>
@@ -477,7 +541,7 @@
     </r>
     <r>
       <rPr>
-        <sz val="10"/>
+        <sz val="12"/>
         <rFont val="Google Sans Text"/>
         <family val="2"/>
       </rPr>
@@ -498,7 +562,7 @@
     </r>
     <r>
       <rPr>
-        <sz val="10"/>
+        <sz val="12"/>
         <rFont val="Google Sans Text"/>
         <family val="2"/>
       </rPr>
@@ -527,7 +591,7 @@
     </r>
     <r>
       <rPr>
-        <sz val="10"/>
+        <sz val="12"/>
         <rFont val="Google Sans Text"/>
         <family val="2"/>
       </rPr>
@@ -544,7 +608,7 @@
   </si>
   <si>
     <r>
-      <t>32</t>
+      <t>carnivore_animation.gd</t>
     </r>
     <r>
       <rPr>
@@ -552,12 +616,20 @@
         <rFont val="Arial"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve"> (Initial)</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>eating_timer -= 1</t>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="Google Sans Text"/>
+        <family val="2"/>
+      </rPr>
+      <t>guppy_feeding.gd</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>1.0</t>
     </r>
     <r>
       <rPr>
@@ -565,108 +637,130 @@
         <rFont val="Arial"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve"> every 2-4 frames</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>carnivore_animation.gd</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">, </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
+      <t xml:space="preserve"> to </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
         <rFont val="Google Sans Text"/>
         <family val="2"/>
       </rPr>
-      <t>guppy_feeding.gd</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>hunger_anim_timer</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> check</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>1.0</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> to </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Google Sans Text"/>
-        <family val="2"/>
-      </rPr>
       <t>1.2</t>
     </r>
   </si>
   <si>
-    <t>Fishbase</t>
-  </si>
-  <si>
-    <t>Idle Deceleration Multiplier</t>
-  </si>
-  <si>
-    <t>1.0, 1.3</t>
-  </si>
-  <si>
-    <t>0.6, 1.0</t>
-  </si>
-  <si>
-    <t>Border</t>
-  </si>
-  <si>
-    <t>Original Pixel Value</t>
-  </si>
-  <si>
-    <t>Logic</t>
-  </si>
-  <si>
-    <t>Left</t>
-  </si>
-  <si>
-    <t>To prevent the nose from clipping the edge.</t>
-  </si>
-  <si>
-    <t>Right</t>
-  </si>
-  <si>
-    <t>(640 total - 20)</t>
-  </si>
-  <si>
-    <t>Top</t>
-  </si>
-  <si>
-    <t>Leaves room for the Menu/Top Bar.</t>
-  </si>
-  <si>
-    <t>Bottom</t>
-  </si>
-  <si>
-    <t>(480 total - 20) Leaves room for the sand.</t>
+    <t>Level 1 logic, passing condition</t>
+  </si>
+  <si>
+    <t>Food type &amp; number upgrade</t>
+  </si>
+  <si>
+    <t>Carnivore update</t>
+  </si>
+  <si>
+    <t>First 5 pets?</t>
+  </si>
+  <si>
+    <t>Chemical potion, chemical guppy</t>
+  </si>
+  <si>
+    <t>Starcatcher</t>
+  </si>
+  <si>
+    <t>First enemy (slyvester), entering animation, enemy moving logic</t>
+  </si>
+  <si>
+    <t>Weapon animation, types, enemy logic, continuous click</t>
+  </si>
+  <si>
+    <t>Gus</t>
+  </si>
+  <si>
+    <t>Balrog</t>
+  </si>
+  <si>
+    <t>Destructor</t>
+  </si>
+  <si>
+    <t>Pet 6-10</t>
+  </si>
+  <si>
+    <t>Beetlemuncher</t>
+  </si>
+  <si>
+    <t>Ulysses</t>
+  </si>
+  <si>
+    <t>Psychosquid</t>
+  </si>
+  <si>
+    <t>First pet (snail), pet system (basic logic, etc)</t>
+  </si>
+  <si>
+    <t>Guppycruncher</t>
+  </si>
+  <si>
+    <t>Pet 11-15</t>
+  </si>
+  <si>
+    <t>Breeder</t>
+  </si>
+  <si>
+    <t>Bilaterus</t>
+  </si>
+  <si>
+    <t>Ultravore</t>
+  </si>
+  <si>
+    <t>Cyrax</t>
+  </si>
+  <si>
+    <t>Pet 15-20</t>
+  </si>
+  <si>
+    <t>Minislyvester</t>
+  </si>
+  <si>
+    <t>Pet 21-24</t>
+  </si>
+  <si>
+    <t>Other modes</t>
+  </si>
+  <si>
+    <t>UI Implementation</t>
+  </si>
+  <si>
+    <t>Virtual Tank</t>
+  </si>
+  <si>
+    <t>Sandbox mode, easter eggs</t>
+  </si>
+  <si>
+    <t>Other stuff</t>
+  </si>
+  <si>
+    <t>fix basic issues (swimming, animation etc)</t>
+  </si>
+  <si>
+    <t>First finish line</t>
+  </si>
+  <si>
+    <t>Second finish line</t>
+  </si>
+  <si>
+    <t>3rd finish line</t>
+  </si>
+  <si>
+    <t>4th</t>
+  </si>
+  <si>
+    <t>5th</t>
+  </si>
+  <si>
+    <t>6th</t>
+  </si>
+  <si>
+    <t>Current</t>
   </si>
 </sst>
 </file>
@@ -683,11 +777,6 @@
     <font>
       <sz val="12"/>
       <name val="Arial"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Google Sans Text"/>
       <family val="2"/>
     </font>
     <font>
@@ -708,13 +797,24 @@
       <name val="Calibri"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="12"/>
+      <name val="Google Sans Text"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -729,12 +829,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1068,6 +1169,313 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D5AEB3FC-A5C3-DD4B-A485-1F6F04CB19D5}">
+  <dimension ref="A1:G31"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
+  <sheetData>
+    <row r="1" spans="1:7">
+      <c r="A1" s="5">
+        <v>0</v>
+      </c>
+      <c r="B1" s="5" t="s">
+        <v>147</v>
+      </c>
+      <c r="C1" s="5"/>
+      <c r="D1" s="5"/>
+      <c r="E1" s="5"/>
+      <c r="F1" s="5"/>
+      <c r="G1" s="5" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7">
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="B2" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7">
+      <c r="A3">
+        <v>2</v>
+      </c>
+      <c r="B3" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7">
+      <c r="A4" s="5">
+        <v>3</v>
+      </c>
+      <c r="B4" s="5" t="s">
+        <v>119</v>
+      </c>
+      <c r="C4" s="5"/>
+      <c r="D4" s="5"/>
+      <c r="E4" s="5"/>
+      <c r="F4" s="5"/>
+      <c r="G4" s="5" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7">
+      <c r="A5">
+        <v>4</v>
+      </c>
+      <c r="B5" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7">
+      <c r="A6">
+        <v>5</v>
+      </c>
+      <c r="B6" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7">
+      <c r="A7" s="5">
+        <v>6</v>
+      </c>
+      <c r="B7" s="5" t="s">
+        <v>132</v>
+      </c>
+      <c r="C7" s="5"/>
+      <c r="D7" s="5"/>
+      <c r="E7" s="5"/>
+      <c r="F7" s="5"/>
+      <c r="G7" s="5" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7">
+      <c r="A8">
+        <v>7</v>
+      </c>
+      <c r="B8" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7">
+      <c r="A9" s="5">
+        <v>8</v>
+      </c>
+      <c r="B9" s="5" t="s">
+        <v>120</v>
+      </c>
+      <c r="C9" s="5"/>
+      <c r="D9" s="5"/>
+      <c r="E9" s="5"/>
+      <c r="F9" s="5"/>
+      <c r="G9" s="5" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7">
+      <c r="A10">
+        <v>9</v>
+      </c>
+      <c r="B10" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7">
+      <c r="A11">
+        <v>10</v>
+      </c>
+      <c r="B11" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7">
+      <c r="A12" s="5">
+        <v>11</v>
+      </c>
+      <c r="B12" s="5" t="s">
+        <v>128</v>
+      </c>
+      <c r="C12" s="5"/>
+      <c r="D12" s="5"/>
+      <c r="E12" s="5"/>
+      <c r="F12" s="5"/>
+      <c r="G12" s="5" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7">
+      <c r="A13">
+        <v>12</v>
+      </c>
+      <c r="B13" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7">
+      <c r="A14" s="5">
+        <v>13</v>
+      </c>
+      <c r="B14" s="5" t="s">
+        <v>127</v>
+      </c>
+      <c r="C14" s="5"/>
+      <c r="D14" s="5"/>
+      <c r="E14" s="5"/>
+      <c r="F14" s="5"/>
+      <c r="G14" s="5" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7">
+      <c r="A15">
+        <v>14</v>
+      </c>
+      <c r="B15" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7">
+      <c r="A16">
+        <v>15</v>
+      </c>
+      <c r="B16" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7">
+      <c r="A17">
+        <v>16</v>
+      </c>
+      <c r="B17" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7">
+      <c r="A18" s="5">
+        <v>17</v>
+      </c>
+      <c r="B18" s="5" t="s">
+        <v>131</v>
+      </c>
+      <c r="C18" s="5"/>
+      <c r="D18" s="5"/>
+      <c r="E18" s="5"/>
+      <c r="F18" s="5"/>
+      <c r="G18" s="5" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7">
+      <c r="A19">
+        <v>18</v>
+      </c>
+      <c r="B19" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7">
+      <c r="A20">
+        <v>19</v>
+      </c>
+      <c r="B20" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7">
+      <c r="A21">
+        <v>20</v>
+      </c>
+      <c r="B21" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7">
+      <c r="A22">
+        <v>21</v>
+      </c>
+      <c r="B22" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7">
+      <c r="A23">
+        <v>22</v>
+      </c>
+      <c r="B23" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7">
+      <c r="A24">
+        <v>23</v>
+      </c>
+      <c r="B24" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7">
+      <c r="A25">
+        <v>24</v>
+      </c>
+      <c r="B25" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7">
+      <c r="A26">
+        <v>25</v>
+      </c>
+      <c r="B26" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7">
+      <c r="A27">
+        <v>26</v>
+      </c>
+      <c r="B27" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7">
+      <c r="A28">
+        <v>27</v>
+      </c>
+      <c r="B28" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7">
+      <c r="A29">
+        <v>28</v>
+      </c>
+      <c r="B29" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7">
+      <c r="A30">
+        <v>29</v>
+      </c>
+      <c r="B30" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7">
+      <c r="A31">
+        <v>30</v>
+      </c>
+      <c r="B31" t="s">
+        <v>146</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EC3AD750-CC70-EF4A-B38E-25EE821561AE}">
   <dimension ref="A1:G21"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
@@ -1108,11 +1516,9 @@
         <v>7</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>110</v>
-      </c>
-      <c r="C2" s="2">
-        <v>0.97499999999999998</v>
-      </c>
+        <v>96</v>
+      </c>
+      <c r="C2" s="2"/>
       <c r="D2" s="2">
         <v>26</v>
       </c>
@@ -1131,10 +1537,7 @@
       <c r="B3" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="C3" s="2">
-        <f>-0.1 / 0.1</f>
-        <v>-1</v>
-      </c>
+      <c r="C3" s="2"/>
       <c r="D3" s="2" t="s">
         <v>11</v>
       </c>
@@ -1155,9 +1558,7 @@
       <c r="B4" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="C4" s="2" t="s">
-        <v>51</v>
-      </c>
+      <c r="C4" s="2"/>
       <c r="D4" s="2" t="s">
         <v>15</v>
       </c>
@@ -1178,9 +1579,7 @@
       <c r="B5" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="C5" s="2">
-        <v>39</v>
-      </c>
+      <c r="C5" s="2"/>
       <c r="D5" s="2" t="s">
         <v>18</v>
       </c>
@@ -1191,7 +1590,7 @@
         <v>19</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -1201,9 +1600,7 @@
       <c r="B6" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="C6" s="2" t="s">
-        <v>53</v>
-      </c>
+      <c r="C6" s="2"/>
       <c r="D6" s="2">
         <v>24</v>
       </c>
@@ -1224,9 +1621,7 @@
       <c r="B7" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="C7" s="2" t="s">
-        <v>111</v>
-      </c>
+      <c r="C7" s="2"/>
       <c r="D7" s="2" t="s">
         <v>26</v>
       </c>
@@ -1245,9 +1640,7 @@
       <c r="B8" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="C8" s="2" t="s">
-        <v>112</v>
-      </c>
+      <c r="C8" s="2"/>
       <c r="D8" s="2" t="s">
         <v>29</v>
       </c>
@@ -1266,9 +1659,7 @@
       <c r="B9" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="C9" s="2">
-        <v>4</v>
-      </c>
+      <c r="C9" s="2"/>
       <c r="D9" s="2" t="s">
         <v>32</v>
       </c>
@@ -1279,7 +1670,7 @@
         <v>33</v>
       </c>
       <c r="G9" s="1" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -1289,9 +1680,7 @@
       <c r="B10" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="C10" s="2" t="s">
-        <v>55</v>
-      </c>
+      <c r="C10" s="2"/>
       <c r="D10" s="2">
         <v>10</v>
       </c>
@@ -1312,9 +1701,7 @@
       <c r="B11" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="C11" s="2" t="s">
-        <v>56</v>
-      </c>
+      <c r="C11" s="2"/>
       <c r="D11" s="2">
         <v>16</v>
       </c>
@@ -1335,9 +1722,7 @@
       <c r="B12" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="C12" s="2">
-        <v>0.65</v>
-      </c>
+      <c r="C12" s="2"/>
       <c r="D12" s="2" t="s">
         <v>26</v>
       </c>
@@ -1358,9 +1743,7 @@
       <c r="B13" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="C13" s="2">
-        <v>6</v>
-      </c>
+      <c r="C13" s="2"/>
       <c r="D13" s="2" t="s">
         <v>26</v>
       </c>
@@ -1371,7 +1754,7 @@
         <v>43</v>
       </c>
       <c r="G13" s="1" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -1381,9 +1764,7 @@
       <c r="B14" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="C14" s="2" t="s">
-        <v>58</v>
-      </c>
+      <c r="C14" s="2"/>
       <c r="D14" s="2">
         <v>8</v>
       </c>
@@ -1404,9 +1785,7 @@
       <c r="B15" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="C15" s="2">
-        <v>40</v>
-      </c>
+      <c r="C15" s="2"/>
       <c r="D15" s="2">
         <v>65</v>
       </c>
@@ -1422,57 +1801,57 @@
     </row>
     <row r="17" spans="1:3">
       <c r="A17" s="3" t="s">
-        <v>113</v>
+        <v>97</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>114</v>
+        <v>98</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>115</v>
+        <v>99</v>
       </c>
     </row>
     <row r="18" spans="1:3">
       <c r="A18" s="3" t="s">
-        <v>116</v>
-      </c>
-      <c r="B18" s="4">
+        <v>100</v>
+      </c>
+      <c r="B18">
         <v>20</v>
       </c>
-      <c r="C18" s="4" t="s">
-        <v>117</v>
+      <c r="C18" t="s">
+        <v>101</v>
       </c>
     </row>
     <row r="19" spans="1:3">
       <c r="A19" s="3" t="s">
-        <v>118</v>
-      </c>
-      <c r="B19" s="4">
+        <v>102</v>
+      </c>
+      <c r="B19">
         <v>620</v>
       </c>
-      <c r="C19" s="4" t="s">
-        <v>119</v>
+      <c r="C19" t="s">
+        <v>103</v>
       </c>
     </row>
     <row r="20" spans="1:3">
       <c r="A20" s="3" t="s">
-        <v>120</v>
-      </c>
-      <c r="B20" s="4">
+        <v>104</v>
+      </c>
+      <c r="B20">
         <v>60</v>
       </c>
-      <c r="C20" s="4" t="s">
-        <v>121</v>
+      <c r="C20" t="s">
+        <v>105</v>
       </c>
     </row>
     <row r="21" spans="1:3">
       <c r="A21" s="3" t="s">
-        <v>122</v>
-      </c>
-      <c r="B21" s="4">
+        <v>106</v>
+      </c>
+      <c r="B21">
         <v>460</v>
       </c>
-      <c r="C21" s="4" t="s">
-        <v>123</v>
+      <c r="C21" t="s">
+        <v>107</v>
       </c>
     </row>
   </sheetData>
@@ -1480,7 +1859,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1631E7DF-1B7D-BA45-B24E-D6899578C313}">
   <dimension ref="A1:H10"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
@@ -1493,17 +1872,18 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8">
+      <c r="A1" s="4"/>
       <c r="B1" s="2" t="s">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>62</v>
+        <v>57</v>
       </c>
       <c r="F1" s="2" t="s">
         <v>4</v>
@@ -1514,206 +1894,210 @@
       <c r="H1" s="2"/>
     </row>
     <row r="2" spans="1:8">
-      <c r="A2" t="s">
+      <c r="A2" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="E2" s="2" t="s">
         <v>109</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="F2" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="H2" s="2"/>
+    </row>
+    <row r="3" spans="1:8">
+      <c r="A3" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="C3" s="2" t="s">
         <v>63</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="D3" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="D2" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="E2" s="2" t="s">
-        <v>98</v>
-      </c>
-      <c r="F2" s="2" t="s">
+      <c r="E3" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="G3" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="G2" s="2" t="s">
+      <c r="H3" s="2"/>
+    </row>
+    <row r="4" spans="1:8">
+      <c r="A4" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="B4" s="2" t="s">
         <v>66</v>
       </c>
-      <c r="H2" s="2"/>
-    </row>
-    <row r="3" spans="1:8">
-      <c r="A3" t="s">
-        <v>109</v>
-      </c>
-      <c r="B3" s="2" t="s">
+      <c r="C4" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="C3" s="2" t="s">
+      <c r="D4" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="E4" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="D3" s="2" t="s">
+      <c r="F4" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="G4" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="H4" s="2"/>
+    </row>
+    <row r="5" spans="1:8">
+      <c r="A5" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="B5" s="2" t="s">
         <v>69</v>
       </c>
-      <c r="E3" s="2" t="s">
-        <v>99</v>
-      </c>
-      <c r="F3" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="G3" s="2" t="s">
+      <c r="C5" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="H3" s="2"/>
-    </row>
-    <row r="4" spans="1:8">
-      <c r="A4" t="s">
-        <v>109</v>
-      </c>
-      <c r="B4" s="2" t="s">
+      <c r="D5" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="E5" s="2" t="s">
         <v>71</v>
       </c>
-      <c r="C4" s="2" t="s">
+      <c r="F5" s="2" t="s">
         <v>72</v>
       </c>
-      <c r="D4" s="2" t="s">
-        <v>100</v>
-      </c>
-      <c r="E4" s="2" t="s">
+      <c r="G5" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="H5" s="2"/>
+    </row>
+    <row r="6" spans="1:8">
+      <c r="A6" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="B6" s="2" t="s">
         <v>73</v>
       </c>
-      <c r="F4" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="G4" s="2" t="s">
-        <v>101</v>
-      </c>
-      <c r="H4" s="2"/>
-    </row>
-    <row r="5" spans="1:8">
-      <c r="A5" t="s">
-        <v>20</v>
-      </c>
-      <c r="B5" s="2" t="s">
+      <c r="C6" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="E6" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="C5" s="2" t="s">
+      <c r="F6" s="2" t="s">
         <v>75</v>
       </c>
-      <c r="D5" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="E5" s="2" t="s">
+      <c r="G6" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="H6" s="2"/>
+    </row>
+    <row r="7" spans="1:8">
+      <c r="A7" s="4"/>
+      <c r="B7" s="2" t="s">
         <v>76</v>
       </c>
-      <c r="F5" s="2" t="s">
+      <c r="C7" s="2" t="s">
         <v>77</v>
       </c>
-      <c r="G5" s="2" t="s">
-        <v>102</v>
-      </c>
-      <c r="H5" s="2"/>
-    </row>
-    <row r="6" spans="1:8">
-      <c r="A6" t="s">
-        <v>38</v>
-      </c>
-      <c r="B6" s="2" t="s">
+      <c r="D7" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="E7" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="F7" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="G7" s="2" t="s">
         <v>78</v>
       </c>
-      <c r="C6" s="2" t="s">
-        <v>75</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="E6" s="2" t="s">
+      <c r="H7" s="2"/>
+    </row>
+    <row r="8" spans="1:8">
+      <c r="A8" s="4"/>
+      <c r="B8" s="2" t="s">
         <v>79</v>
       </c>
-      <c r="F6" s="2" t="s">
+      <c r="C8" s="2" t="s">
         <v>80</v>
       </c>
-      <c r="G6" s="2" t="s">
-        <v>103</v>
-      </c>
-      <c r="H6" s="2"/>
-    </row>
-    <row r="7" spans="1:8">
-      <c r="B7" s="2" t="s">
+      <c r="D8" s="2" t="s">
         <v>81</v>
       </c>
-      <c r="C7" s="2" t="s">
+      <c r="E8" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="F8" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="G8" s="2" t="s">
         <v>82</v>
       </c>
-      <c r="D7" s="2" t="s">
-        <v>104</v>
-      </c>
-      <c r="E7" s="2" t="s">
-        <v>105</v>
-      </c>
-      <c r="F7" s="2" t="s">
-        <v>106</v>
-      </c>
-      <c r="G7" s="2" t="s">
+      <c r="H8" s="2"/>
+    </row>
+    <row r="9" spans="1:8">
+      <c r="A9" s="4"/>
+      <c r="B9" s="2" t="s">
         <v>83</v>
       </c>
-      <c r="H7" s="2"/>
-    </row>
-    <row r="8" spans="1:8">
-      <c r="B8" s="2" t="s">
+      <c r="C9" s="2" t="s">
         <v>84</v>
       </c>
-      <c r="C8" s="2" t="s">
+      <c r="D9" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="E9" s="2" t="s">
         <v>85</v>
       </c>
-      <c r="D8" s="2" t="s">
+      <c r="F9" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="G9" s="2" t="s">
         <v>86</v>
       </c>
-      <c r="E8" s="2" t="s">
-        <v>107</v>
-      </c>
-      <c r="F8" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="G8" s="2" t="s">
+      <c r="H9" s="2"/>
+    </row>
+    <row r="10" spans="1:8">
+      <c r="A10" s="4"/>
+      <c r="B10" s="2" t="s">
         <v>87</v>
       </c>
-      <c r="H8" s="2"/>
-    </row>
-    <row r="9" spans="1:8">
-      <c r="B9" s="2" t="s">
+      <c r="C10" s="2" t="s">
         <v>88</v>
       </c>
-      <c r="C9" s="2" t="s">
+      <c r="D10" s="2" t="s">
         <v>89</v>
       </c>
-      <c r="D9" s="2" t="s">
-        <v>108</v>
-      </c>
-      <c r="E9" s="2" t="s">
+      <c r="E10" s="2" t="s">
         <v>90</v>
-      </c>
-      <c r="F9" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="G9" s="2" t="s">
-        <v>91</v>
-      </c>
-      <c r="H9" s="2"/>
-    </row>
-    <row r="10" spans="1:8">
-      <c r="B10" s="2" t="s">
-        <v>92</v>
-      </c>
-      <c r="C10" s="2" t="s">
-        <v>93</v>
-      </c>
-      <c r="D10" s="2" t="s">
-        <v>94</v>
-      </c>
-      <c r="E10" s="2" t="s">
-        <v>95</v>
       </c>
       <c r="F10" s="2" t="s">
         <v>8</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>96</v>
+        <v>91</v>
       </c>
       <c r="H10" s="2"/>
     </row>
